--- a/Exam/gymtrackerpro/lib/service/__tests__/it/exercise-service/listExercises-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/it/exercise-service/listExercises-it-form.xlsx
@@ -356,7 +356,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="14516100" cy="2019300"/>
+    <xdr:ext cx="14682787" cy="2757487"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -841,7 +841,7 @@
   <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="26" width="11" customWidth="1"/>
+    <col min="1" max="27" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
